--- a/projects/01_tau_asymmetry/media/xs_demographics.xlsx
+++ b/projects/01_tau_asymmetry/media/xs_demographics.xlsx
@@ -474,14 +474,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr"/>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Grouped by temporal_meta_tau_asymmetry_group</t>
+          <t>Grouped by temporal_meta_tau_asymmetry_group_v2</t>
         </is>
       </c>
       <c r="D1" s="1" t="n"/>
@@ -590,7 +590,9 @@
           <t>M</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>46 (45.10)</t>
@@ -682,38 +684,40 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Diagnosis, n (%)</t>
+          <t>Handedness, n (%)</t>
         </is>
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>CU</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>42</v>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>11 (10.78)</t>
+          <t>85 (94.44)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>40 (13.07)</t>
+          <t>262 (93.91)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>9 (20.45)</t>
+          <t>41 (100.00)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.511</t>
+          <t>0.567</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Chi-squared</t>
+          <t>Chi-squared (warning: expected count &lt; 5)</t>
         </is>
       </c>
     </row>
@@ -721,25 +725,21 @@
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>MCI</t>
+          <t>Left</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>39 (38.24)</t>
+          <t>5 (5.56)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>106 (34.64)</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>12 (27.27)</t>
-        </is>
-      </c>
+          <t>16 (5.73)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -747,171 +747,149 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>AD</t>
+          <t>Ambidextrous</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>52 (50.98)</t>
-        </is>
-      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>160 (52.29)</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>23 (52.27)</t>
-        </is>
-      </c>
+          <t>1 (0.36)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Temporal tau load, median [Q1,Q3]</t>
-        </is>
-      </c>
-      <c r="B12" s="1" t="inlineStr"/>
+          <t>Diagnosis, n (%)</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>CU</t>
+        </is>
+      </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.92 [1.67,2.27]</t>
+          <t>11 (10.78)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.71 [1.45,2.33]</t>
+          <t>40 (13.07)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2.07 [1.80,2.73]</t>
+          <t>9 (20.45)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>&lt;0.001</t>
+          <t>0.511</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Kruskal-Wallis</t>
+          <t>Chi-squared</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>Temporal tau laterality index, mean (SD)</t>
-        </is>
-      </c>
-      <c r="B13" s="1" t="inlineStr"/>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>MCI</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>14.41 (3.67)</t>
+          <t>39 (38.24)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4.24 (2.39)</t>
+          <t>106 (34.64)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>14.66 (5.42)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>One-way ANOVA</t>
-        </is>
-      </c>
+          <t>12 (27.27)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Neocortical Aβ load, mean (SD)</t>
-        </is>
-      </c>
-      <c r="B14" s="1" t="inlineStr"/>
-      <c r="C14" t="n">
-        <v>219</v>
-      </c>
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.59 (0.20)</t>
+          <t>52 (50.98)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.63 (0.23)</t>
+          <t>160 (52.29)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1.56 (0.23)</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0.211</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>One-way ANOVA</t>
-        </is>
-      </c>
+          <t>23 (52.27)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>ApoE4 count, n (%)</t>
+          <t>Clinical phenotype, n (%)</t>
         </is>
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>32 (31.37)</t>
+          <t>8 (7.84)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>75 (24.51)</t>
+          <t>40 (13.07)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>16 (36.36)</t>
+          <t>9 (20.45)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>0.157</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Chi-squared</t>
+          <t>Chi-squared (warning: expected count &lt; 5)</t>
         </is>
       </c>
     </row>
@@ -919,23 +897,23 @@
       <c r="A16" s="1" t="n"/>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>aAD</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>49 (48.04)</t>
+          <t>89 (87.25)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>182 (59.48)</t>
+          <t>254 (83.01)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>21 (47.73)</t>
+          <t>35 (79.55)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -945,135 +923,93 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>lvPPA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>21 (20.59)</t>
+          <t>4 (3.92)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>49 (16.01)</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>7 (15.91)</t>
-        </is>
-      </c>
+          <t>3 (0.98)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>MMSE, median [Q1,Q3]</t>
-        </is>
-      </c>
-      <c r="B18" s="1" t="inlineStr"/>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>PCA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>24.00 [21.00,27.00]</t>
+          <t>1 (0.98)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>25.00 [21.00,27.00]</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>26.00 [22.75,28.00]</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>0.328</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Kruskal-Wallis</t>
-        </is>
-      </c>
+          <t>7 (2.29)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>mPACC, median [Q1,Q3]</t>
-        </is>
-      </c>
-      <c r="B19" s="1" t="inlineStr"/>
-      <c r="C19" t="n">
-        <v>42</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>-2.69 [-4.02,-1.68]</t>
-        </is>
-      </c>
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>bvAD</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>-2.56 [-3.78,-1.52]</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>-2.47 [-3.92,-1.24]</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>0.568</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kruskal-Wallis</t>
-        </is>
-      </c>
+          <t>2 (0.65)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Has RSfMRI, n (%)</t>
+          <t>Braak stage, n (%)</t>
         </is>
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>29 (28.43)</t>
-        </is>
-      </c>
+          <t>I-II</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>91 (29.74)</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>14 (31.82)</t>
-        </is>
-      </c>
+          <t>11 (3.59)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.917</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Chi-squared</t>
+          <t>Chi-squared (warning: expected count &lt; 5)</t>
         </is>
       </c>
     </row>
@@ -1081,162 +1017,332 @@
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>III-IV</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>73 (71.57)</t>
+          <t>21 (20.59)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>215 (70.26)</t>
+          <t>107 (34.97)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>30 (68.18)</t>
+          <t>6 (13.64)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Has dMRI, n (%)</t>
-        </is>
-      </c>
+      <c r="A22" s="1" t="n"/>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>V-VI</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>21 (20.59)</t>
+          <t>81 (79.41)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>71 (23.20)</t>
+          <t>188 (61.44)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>8 (18.18)</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0.690</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Chi-squared</t>
-        </is>
-      </c>
+          <t>38 (86.36)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>Temporal tau load, median [Q1,Q3]</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="inlineStr"/>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>81 (79.41)</t>
+          <t>1.92 [1.67,2.27]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>235 (76.80)</t>
+          <t>1.71 [1.45,2.33]</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>36 (81.82)</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+          <t>2.07 [1.80,2.73]</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Kruskal-Wallis</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Has Aβ-PET, n (%)</t>
-        </is>
-      </c>
-      <c r="B24" s="1" t="inlineStr">
+          <t>Temporal tau LI, mean (SD)</t>
+        </is>
+      </c>
+      <c r="B24" s="1" t="inlineStr"/>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>14.41 (3.67)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>4.24 (2.39)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>14.66 (5.42)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>One-way ANOVA</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Neocortical Aβ load, mean (SD)</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="inlineStr"/>
+      <c r="C25" t="n">
+        <v>219</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1.59 (0.20)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1.63 (0.23)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1.56 (0.23)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0.211</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>One-way ANOVA</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>ApoE4, n (%)</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>50 (49.02)</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>149 (48.69)</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>20 (45.45)</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>0.915</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>32 (31.37)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>75 (24.51)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>16 (36.36)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>0.188</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
         <is>
           <t>Chi-squared</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="n"/>
-      <c r="B25" s="1" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>52 (50.98)</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>157 (51.31)</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>24 (54.55)</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>49 (48.04)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>182 (59.48)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>21 (47.73)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n"/>
+      <c r="B28" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>21 (20.59)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>49 (16.01)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>7 (15.91)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>MMSE, median [Q1,Q3]</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="inlineStr"/>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>24.00 [21.00,27.00]</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>25.00 [21.00,27.00]</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>26.00 [22.75,28.00]</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>0.328</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Kruskal-Wallis</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>mPACC, median [Q1,Q3]</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="inlineStr"/>
+      <c r="C30" t="n">
+        <v>42</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>-2.69 [-4.02,-1.68]</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>-2.56 [-3.78,-1.52]</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>-2.47 [-3.92,-1.24]</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>0.568</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Kruskal-Wallis</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A15:A17"/>
-    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="A15:A19"/>
+    <mergeCell ref="A20:A22"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="C1:H1"/>
